--- a/Dashboard_Fundos.xlsx
+++ b/Dashboard_Fundos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\estudos\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75984334-4D8A-483E-B329-8C239B428739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C47A079-9B5F-4B09-ADF1-9E22DE2F8CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="14610" windowHeight="15480" tabRatio="345" xr2:uid="{D63472A4-8300-4934-9C87-0EC792DCF89D}"/>
+    <workbookView xWindow="3120" yWindow="720" windowWidth="14610" windowHeight="15480" tabRatio="345" xr2:uid="{D63472A4-8300-4934-9C87-0EC792DCF89D}"/>
   </bookViews>
   <sheets>
     <sheet name="APP" sheetId="1" r:id="rId1"/>
@@ -788,45 +788,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -850,9 +811,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -860,11 +818,53 @@
     <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1284,7 +1284,7 @@
             <c:numRef>
               <c:f>APP!$C$36:$C$41</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0.32</c:v>
@@ -2376,28 +2376,28 @@
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="2:4" ht="17.25">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="32"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="23">
         <v>2000</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="17.25">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="24">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="18" thickBot="1">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="41"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="25">
         <f>D12*30%</f>
         <v>600</v>
@@ -2405,54 +2405,54 @@
     </row>
     <row r="15" spans="2:4" ht="15" thickBot="1"/>
     <row r="16" spans="2:4" ht="28.5" customHeight="1">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:6" ht="17.25">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="32"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="18">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17.25">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="34"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17.25">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="20">
         <v>1.0789999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.25">
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="43"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="21">
         <f>FV(taxa_mensal,qtd_anos*12,aporte*-1)</f>
         <v>16755.382799697527</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" thickBot="1">
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="36"/>
+      <c r="C21" s="58"/>
       <c r="D21" s="22">
         <f>patrimonio*rendimento_carteira</f>
         <v>100.53229679818516</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1"/>
     <row r="23" spans="1:6" ht="30.75">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="38"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="8" t="s">
         <v>12</v>
       </c>
@@ -2551,118 +2551,118 @@
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1"/>
     <row r="32" spans="1:6" ht="15">
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="50"/>
+      <c r="D32" s="37"/>
     </row>
     <row r="33" spans="2:4" ht="15.75" thickBot="1">
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="52">
+      <c r="C33" s="39">
         <f>aporte</f>
         <v>200</v>
       </c>
-      <c r="D33" s="53"/>
+      <c r="D33" s="40"/>
     </row>
     <row r="34" spans="2:4" ht="15" thickBot="1"/>
     <row r="35" spans="2:4" ht="15">
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="33" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="16.5">
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B36,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.32</v>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="60">
         <f>C36*$C$33</f>
         <v>64</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="16.5">
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B37,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.35</v>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="60">
         <f t="shared" ref="D37:D41" si="0">C37*$C$33</f>
         <v>70</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="16.5">
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B38,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.08</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="60">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="16.5">
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="59">
+      <c r="C39" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B39,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.05</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="60">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="16.5">
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="59">
+      <c r="C40" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B40,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="60">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="16.5">
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="59">
+      <c r="C41" s="61">
         <f>VLOOKUP($C$32&amp;"-"&amp;B41,Planilha2!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="60">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="15.75" thickBot="1">
-      <c r="B42" s="47"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="61">
+      <c r="B42" s="34"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="46">
         <f>SUM(D36:D41)</f>
         <v>200</v>
       </c>
@@ -2830,17 +2830,17 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="56" t="str">
+      <c r="A10" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Moderado-TIJOLO</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="44">
         <v>0.35</v>
       </c>
     </row>
@@ -3003,12 +3003,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3267,20 +3269,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C32110DE-3D77-470C-9CED-65521C30E3F6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D0D6DD-E6DB-45C8-8F90-E314C090C085}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3305,12 +3308,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D0D6DD-E6DB-45C8-8F90-E314C090C085}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C32110DE-3D77-470C-9CED-65521C30E3F6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
-    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>